--- a/datasets/treinamento.xlsx
+++ b/datasets/treinamento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,37 +467,1345 @@
           <t>Y_5</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1.3719</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7022</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.8535</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.7909</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.6445</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5687</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-1.7163</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.6283</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.1434</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6637</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2606</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.3749</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.5071</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.3009</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.7221</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.7587</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7681</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5592</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.8072</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5154</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3129</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>-0.5231</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.5776</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7112000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.1209</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.3915</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.2291</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.1735</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.6081</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.2988</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4778</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8649</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.7359</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1869</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.0872</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.3584</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.7115</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.1469</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9573</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.8250999999999999</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.284</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8452</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.2382</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.7633</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.8249</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.5855</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9137999999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.9792</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.4276</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.5331</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.7286</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0.5971</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.4865</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.6069</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0.8475</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2.1479</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.8235</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1.3967</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.4171</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6443</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.3927</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1.5378</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.7755</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.5668</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7829</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-1.248</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8591</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.8093</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>-0.2479</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.7381</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>-0.3088</v>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.0929</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.5483</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>-0.518</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1.4974</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.3993</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0.6833</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.8266</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.8864</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-1.4066</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.4879</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>-0.1069</v>
+      </c>
+      <c r="B34" t="n">
+        <v>-3.2329</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-2.4572</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.6261</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7304</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.437</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-1_x000d_</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
         <v>0.8298</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B36" t="n">
         <v>-1.4089</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C36" t="n">
         <v>0.3119</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D36" t="n">
         <v>1.3235</v>
       </c>
-      <c r="E2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1</v>
+      <c r="E36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/datasets/treinamento.xlsx
+++ b/datasets/treinamento.xlsx
@@ -799,19 +799,19 @@
         <v>-1</v>
       </c>
       <c r="F10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
@@ -1179,19 +1179,19 @@
         <v>-1</v>
       </c>
       <c r="F20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
@@ -1293,19 +1293,19 @@
         <v>-1</v>
       </c>
       <c r="F23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
@@ -1331,19 +1331,19 @@
         <v>-1</v>
       </c>
       <c r="F24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">

--- a/datasets/treinamento.xlsx
+++ b/datasets/treinamento.xlsx
@@ -799,19 +799,19 @@
         <v>-1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
@@ -1179,19 +1179,19 @@
         <v>-1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
@@ -1293,19 +1293,19 @@
         <v>-1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
@@ -1331,19 +1331,19 @@
         <v>-1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
